--- a/downloads/free-resources/ahqs-competency-assessment-form.xlsx
+++ b/downloads/free-resources/ahqs-competency-assessment-form.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection workbookPassword="AF18" lockStructure="1" lockWindows="0"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -593,7 +593,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -694,7 +694,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -795,7 +795,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -899,7 +899,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -989,7 +989,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1022,7 +1022,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1174,7 +1174,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1201,7 +1201,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1228,7 +1228,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1255,7 +1255,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1280,7 +1280,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1361,7 +1361,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1670,7 +1670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B9:C34"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="22" min="1" max="1"/>
@@ -1678,6 +1678,14 @@
     <col width="3" customWidth="1" style="22" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="26.8" customHeight="1" s="23">
       <c r="B9" s="24" t="inlineStr">
         <is>
@@ -1692,6 +1700,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="23">
       <c r="B12" s="26" t="n"/>
       <c r="C12" s="26" t="n"/>
@@ -1703,6 +1712,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="16.15" customHeight="1" s="23">
       <c r="B15" s="28" t="inlineStr">
         <is>
@@ -1752,6 +1762,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="16.15" customHeight="1" s="23">
       <c r="B23" s="28" t="inlineStr">
         <is>
@@ -1801,6 +1812,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="16.15" customHeight="1" s="23">
       <c r="B31" s="28" t="inlineStr">
         <is>
@@ -1815,6 +1827,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="23">
       <c r="B34" s="31" t="inlineStr">
         <is>
@@ -1823,6 +1836,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1972,6 +1986,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1984,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C20"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="22" min="1" max="1"/>
@@ -1992,6 +2007,7 @@
     <col width="40" customWidth="1" style="22" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="23">
       <c r="B2" s="34" t="inlineStr">
         <is>
@@ -1999,6 +2015,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="23">
       <c r="B4" s="35" t="inlineStr">
         <is>
@@ -2007,6 +2024,7 @@
       </c>
       <c r="C4" s="36" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="24" customHeight="1" s="23">
       <c r="B6" s="35" t="inlineStr">
         <is>
@@ -2015,6 +2033,7 @@
       </c>
       <c r="C6" s="36" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1" s="23">
       <c r="B8" s="35" t="inlineStr">
         <is>
@@ -2023,6 +2042,7 @@
       </c>
       <c r="C8" s="36" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="23">
       <c r="B10" s="35" t="inlineStr">
         <is>
@@ -2031,6 +2051,7 @@
       </c>
       <c r="C10" s="36" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="24" customHeight="1" s="23">
       <c r="B12" s="35" t="inlineStr">
         <is>
@@ -2039,6 +2060,7 @@
       </c>
       <c r="C12" s="36" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="24" customHeight="1" s="23">
       <c r="B14" s="35" t="inlineStr">
         <is>
@@ -2051,6 +2073,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1" s="23">
       <c r="B16" s="35" t="inlineStr">
         <is>
@@ -2059,6 +2082,7 @@
       </c>
       <c r="C16" s="36" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="23">
       <c r="B18" s="35" t="inlineStr">
         <is>
@@ -2067,6 +2091,7 @@
       </c>
       <c r="C18" s="36" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="24" customHeight="1" s="23">
       <c r="B20" s="35" t="inlineStr">
         <is>
@@ -2076,6 +2101,7 @@
       <c r="C20" s="36" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
@@ -2765,6 +2791,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <autoFilter ref="A1:J20"/>
   <conditionalFormatting sqref="E2:E20">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
@@ -2799,13 +2826,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="22" min="1" max="1"/>
     <col width="14" customWidth="1" style="22" min="2" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="31.5" customHeight="1" s="23">
       <c r="B2" s="34" t="inlineStr">
         <is>
@@ -2813,6 +2841,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="23">
       <c r="B4" s="41" t="inlineStr">
         <is>
@@ -2863,6 +2892,8 @@
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" s="23"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="24" customHeight="1" s="23">
       <c r="B9" s="43" t="inlineStr">
         <is>
@@ -3064,6 +3095,11 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="24" customHeight="1" s="23">
       <c r="B22" s="43" t="inlineStr">
         <is>
@@ -3149,6 +3185,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <mergeCells count="13">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="J4:K4"/>
